--- a/excel/2020_指标、阈值及数据-2020年.xlsx
+++ b/excel/2020_指标、阈值及数据-2020年.xlsx
@@ -5,20 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\教育\大学\zz-system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\projects_data\.openclaw\workspace\academic-report\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC415ECF-74E5-4453-A0DE-6724408E7F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D553572-421F-432F-8F9C-5FDEA1EA46EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="飞行器制造技术（飞机制造技术方向" sheetId="2" r:id="rId2"/>
-    <sheet name="机电一体化技术" sheetId="3" r:id="rId3"/>
-    <sheet name="汽车运用与维修技术" sheetId="4" r:id="rId4"/>
-    <sheet name="软件技术" sheetId="5" r:id="rId5"/>
-    <sheet name="计算机网络技术（含中高职贯通）" sheetId="6" r:id="rId6"/>
+    <sheet name="飞行器制造技术（飞机制造技术方向" sheetId="2" r:id="rId1"/>
+    <sheet name="机电一体化技术" sheetId="3" r:id="rId2"/>
+    <sheet name="汽车运用与维修技术" sheetId="4" r:id="rId3"/>
+    <sheet name="软件技术" sheetId="5" r:id="rId4"/>
+    <sheet name="计算机网络技术（含中高职贯通）" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="23">
   <si>
     <t>序号</t>
   </si>
@@ -46,139 +45,46 @@
     <t>指标名称</t>
   </si>
   <si>
-    <t>计算方式/说明</t>
-  </si>
-  <si>
-    <t>预警阈值（红/黄/蓝、绿）</t>
-  </si>
-  <si>
-    <t>(实际录取数/招生计划数)*100%</t>
-  </si>
-  <si>
-    <t>&lt;85% / 85%-90% / &gt;=90%</t>
-  </si>
-  <si>
     <t>生师比</t>
-  </si>
-  <si>
-    <t>折合在校生数/折合教师数</t>
-  </si>
-  <si>
-    <t>&gt;18:1</t>
   </si>
   <si>
     <t>课程优良率</t>
   </si>
   <si>
-    <t>学生评教“优良”课程比例</t>
-  </si>
-  <si>
-    <t>&lt;70% / 70%-85% / &gt;=85%</t>
-  </si>
-  <si>
     <t>技能证书通过率</t>
-  </si>
-  <si>
-    <t>获相关职业资格证书学生比例</t>
-  </si>
-  <si>
-    <t>&lt;60% / 60%-75% / &gt;=75%</t>
   </si>
   <si>
     <t>毕业率</t>
   </si>
   <si>
-    <t>当届毕业生实际毕业比例</t>
-  </si>
-  <si>
-    <t>&lt;95% / 95%-97% / &gt;=97%</t>
-  </si>
-  <si>
     <t>就业去向落实率</t>
-  </si>
-  <si>
-    <t>截止当年底的毕业生就业率</t>
-  </si>
-  <si>
-    <t>&lt;92% / 92%-96% / &gt;=96%</t>
   </si>
   <si>
     <t>专业相关度</t>
   </si>
   <si>
-    <t>就业岗位与专业相关毕业生比例</t>
-  </si>
-  <si>
-    <t>&lt;68% / 68%-70% / &gt;=70%</t>
-  </si>
-  <si>
     <t>在校生满意度</t>
-  </si>
-  <si>
-    <t>在校生对所学专业的满意度。在校生满意度=学生问卷评价总分/问卷作答总人数</t>
-  </si>
-  <si>
-    <t>&lt;91% / 91%-95% / &gt;=95%</t>
   </si>
   <si>
     <t>毕业生满意度</t>
   </si>
   <si>
-    <t>毕业生对所学专业的满意度。</t>
-  </si>
-  <si>
-    <t>&lt;92% / 92%-95% / &gt;=95%</t>
-  </si>
-  <si>
     <t>企业订单学生占比</t>
-  </si>
-  <si>
-    <t>专业接受企业订单，且在该企业就业的学生人数占学生总数的比例。</t>
-  </si>
-  <si>
-    <t>&lt;8% / 8%-15% / &gt;=15%</t>
   </si>
   <si>
     <t>双师型专任教师占比</t>
   </si>
   <si>
-    <t>“双师型”专任教师占专任教师总数的百分比。</t>
-  </si>
-  <si>
     <t>高级职称专任教师占比</t>
-  </si>
-  <si>
-    <t>高级职称的专任教师占专任教师总数的比例。</t>
-  </si>
-  <si>
-    <t>&lt;15% / 15%-25% / &gt;=25%</t>
   </si>
   <si>
     <t>高技术技能人才占比</t>
   </si>
   <si>
-    <t>取得技师、高级技师职业技能等级证书，或取得市、区级及以上杰出技术能手、首席技师资助项目带头人、技能大师工作室带头人等称号的教师数量占专任教师总数的比例。</t>
-  </si>
-  <si>
-    <t>&lt;5% / 5%-10% / &gt;=10%</t>
-  </si>
-  <si>
     <t>师均论文数、著作数、课题数</t>
   </si>
   <si>
-    <t>专任教师在国内外正式学术刊物和出版社以第一作者发表学术论文、出版著作、教材的数量及主持开展院级、市级和国家级课题的数量与专业专任教师总数的比值。</t>
-  </si>
-  <si>
-    <t>&lt;0.5 / 0.5-1 / &gt;=1</t>
-  </si>
-  <si>
     <t>教师人均企业实践时间（天）</t>
-  </si>
-  <si>
-    <t>专任教师每学年到企业进行实践的时间总量（天数）与专业专任教师总数的比值。</t>
-  </si>
-  <si>
-    <t>&lt;18 / 18-30 / &gt;=30</t>
   </si>
   <si>
     <t>权重</t>
@@ -209,8 +115,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
-    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0_ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -434,7 +340,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -459,7 +365,7 @@
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -468,7 +374,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -483,7 +389,7 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -492,7 +398,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -513,7 +419,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -525,7 +431,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -558,7 +464,7 @@
     <xf numFmtId="10" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -579,7 +485,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -591,33 +497,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -630,8 +509,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1112,247 +994,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.54296875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" customWidth="1"/>
-    <col min="3" max="3" width="43.453125" customWidth="1"/>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22">
-        <v>1</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="54" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="22">
-        <v>2</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
-        <v>3</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
-        <v>4</v>
-      </c>
-      <c r="B5" s="53" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22">
-        <v>5</v>
-      </c>
-      <c r="B6" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>6</v>
-      </c>
-      <c r="B7" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22">
-        <v>7</v>
-      </c>
-      <c r="B8" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22">
-        <v>8</v>
-      </c>
-      <c r="B9" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="22">
-        <v>9</v>
-      </c>
-      <c r="B10" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="58" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="22">
-        <v>10</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="58" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
-        <v>11</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="22">
-        <v>12</v>
-      </c>
-      <c r="B13" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="56" x14ac:dyDescent="0.25">
-      <c r="A14" s="22">
-        <v>13</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="58" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="56" x14ac:dyDescent="0.25">
-      <c r="A15" s="22">
-        <v>14</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="58" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="37" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
-        <v>15</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="58" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1368,21 +1009,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="64" t="s">
-        <v>53</v>
+      <c r="B2" s="55" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="6">
         <v>5</v>
@@ -1399,7 +1040,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="6">
         <v>3</v>
@@ -1416,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6">
         <v>3</v>
@@ -1433,7 +1074,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -1450,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6">
         <v>3</v>
@@ -1467,7 +1108,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6">
         <v>5</v>
@@ -1484,7 +1125,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6">
         <v>4</v>
@@ -1501,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C9" s="14">
         <v>4</v>
@@ -1518,7 +1159,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C10" s="14">
         <v>4</v>
@@ -1535,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11" s="14">
         <v>4</v>
@@ -1552,7 +1193,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C12" s="14">
         <v>4</v>
@@ -1569,7 +1210,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C13" s="14">
         <v>4</v>
@@ -1586,7 +1227,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C14" s="14">
         <v>4</v>
@@ -1603,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
@@ -1620,7 +1261,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C16" s="14">
         <v>4</v>
@@ -1633,15 +1274,15 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="59"/>
+      <c r="A17" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="56"/>
       <c r="C17" s="10">
         <v>60</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E17" s="51">
         <f>SUM(E2:E16)</f>
@@ -1665,7 +1306,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1684,21 +1325,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E1" s="36" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="37">
         <v>1</v>
       </c>
-      <c r="B2" s="63" t="s">
-        <v>53</v>
+      <c r="B2" s="54" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="39">
         <v>5</v>
@@ -1715,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="43">
         <v>3</v>
@@ -1732,7 +1373,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="43">
         <v>3</v>
@@ -1749,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" s="43">
         <v>4</v>
@@ -1766,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" s="43">
         <v>3</v>
@@ -1783,7 +1424,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C7" s="43">
         <v>5</v>
@@ -1800,7 +1441,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C8" s="43">
         <v>4</v>
@@ -1817,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C9" s="47">
         <v>4</v>
@@ -1834,7 +1475,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C10" s="47">
         <v>4</v>
@@ -1851,7 +1492,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11" s="47">
         <v>4</v>
@@ -1868,7 +1509,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C12" s="47">
         <v>4</v>
@@ -1885,7 +1526,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C13" s="47">
         <v>4</v>
@@ -1902,7 +1543,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="42" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C14" s="47">
         <v>4</v>
@@ -1919,7 +1560,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="42" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C15" s="47">
         <v>5</v>
@@ -1936,7 +1577,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C16" s="47">
         <v>4</v>
@@ -1949,15 +1590,15 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="59"/>
+      <c r="A17" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="56"/>
       <c r="C17" s="50">
         <v>60</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E17" s="19">
         <f>SUM(E2:E16)</f>
@@ -1981,7 +1622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -2000,21 +1641,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="62" t="s">
-        <v>53</v>
+      <c r="B2" s="53" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="24">
         <v>5</v>
@@ -2031,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="24">
         <v>3</v>
@@ -2048,7 +1689,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="24">
         <v>3</v>
@@ -2065,7 +1706,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" s="24">
         <v>4</v>
@@ -2082,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" s="24">
         <v>3</v>
@@ -2099,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C7" s="24">
         <v>5</v>
@@ -2116,7 +1757,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C8" s="24">
         <v>4</v>
@@ -2133,7 +1774,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C9" s="14">
         <v>4</v>
@@ -2150,7 +1791,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C10" s="14">
         <v>4</v>
@@ -2167,7 +1808,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11" s="14">
         <v>4</v>
@@ -2184,7 +1825,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C12" s="14">
         <v>4</v>
@@ -2201,7 +1842,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C13" s="14">
         <v>4</v>
@@ -2218,7 +1859,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C14" s="14">
         <v>4</v>
@@ -2235,7 +1876,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
@@ -2252,7 +1893,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C16" s="14">
         <v>4</v>
@@ -2265,15 +1906,15 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="60" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="60"/>
+      <c r="A17" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="57"/>
       <c r="C17" s="31">
         <v>60</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E17" s="26">
         <f>SUM(E2:E16)</f>
@@ -2287,6 +1928,315 @@
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" s="35"/>
       <c r="C20" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.36328125" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="6">
+        <v>5</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1.0658000000000001</v>
+      </c>
+      <c r="E2" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="6">
+        <v>3</v>
+      </c>
+      <c r="D3" s="10">
+        <v>16.5</v>
+      </c>
+      <c r="E3" s="11">
+        <f>D3/18*$C$4</f>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6">
+        <v>3</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0.82</v>
+      </c>
+      <c r="E4" s="10">
+        <f>D4/1*$C$6</f>
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.40660000000000002</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="E6" s="10">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6">
+        <v>5</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.92220000000000002</v>
+      </c>
+      <c r="E7" s="8">
+        <v>4.6100000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0.67</v>
+      </c>
+      <c r="E8" s="11">
+        <f>D8/0.7*$C$14</f>
+        <v>3.8285714285714301</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="14">
+        <v>4</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="14">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.93940000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="14">
+        <v>4</v>
+      </c>
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="14">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.83330000000000004</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="14">
+        <v>4</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.16669999999999999</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="14">
+        <v>4</v>
+      </c>
+      <c r="D14" s="17">
+        <v>0</v>
+      </c>
+      <c r="E14" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="14">
+        <v>5</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1.17</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="17">
+        <v>13.5</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="56"/>
+      <c r="C17" s="10">
+        <v>60</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="19">
+        <f>SUM(E2:E16)</f>
+        <v>38.478571428571399</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2298,315 +2248,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="20.36328125" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="6">
-        <v>5</v>
-      </c>
-      <c r="D2" s="7">
-        <v>1.0658000000000001</v>
-      </c>
-      <c r="E2" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6">
-        <v>3</v>
-      </c>
-      <c r="D3" s="10">
-        <v>16.5</v>
-      </c>
-      <c r="E3" s="11">
-        <f>D3/18*$C$4</f>
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6">
-        <v>3</v>
-      </c>
-      <c r="D4" s="12">
-        <v>0.82</v>
-      </c>
-      <c r="E4" s="10">
-        <f>D4/1*$C$6</f>
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.40660000000000002</v>
-      </c>
-      <c r="E5" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="6">
-        <v>3</v>
-      </c>
-      <c r="D6" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="10">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6">
-        <v>5</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.92220000000000002</v>
-      </c>
-      <c r="E7" s="8">
-        <v>4.6100000000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="6">
-        <v>4</v>
-      </c>
-      <c r="D8" s="13">
-        <v>0.67</v>
-      </c>
-      <c r="E8" s="11">
-        <f>D8/0.7*$C$14</f>
-        <v>3.8285714285714301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="14">
-        <v>4</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3.88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="14">
-        <v>4</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0.93940000000000001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="14">
-        <v>4</v>
-      </c>
-      <c r="D11" s="15">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="14">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.83330000000000004</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="14">
-        <v>4</v>
-      </c>
-      <c r="D13" s="7">
-        <v>0.16669999999999999</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="14">
-        <v>4</v>
-      </c>
-      <c r="D14" s="17">
-        <v>0</v>
-      </c>
-      <c r="E14" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="14">
-        <v>5</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1.17</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" s="14">
-        <v>4</v>
-      </c>
-      <c r="D16" s="17">
-        <v>13.5</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="10">
-        <v>60</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E17" s="19">
-        <f>SUM(E2:E16)</f>
-        <v>38.478571428571399</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A17:B17"/>
-  </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -2622,21 +2263,21 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="61" t="s">
-        <v>52</v>
+      <c r="B2" s="52" t="s">
+        <v>21</v>
       </c>
       <c r="C2" s="6">
         <v>5</v>
@@ -2653,7 +2294,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="6">
         <v>3</v>
@@ -2671,7 +2312,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6">
         <v>3</v>
@@ -2689,7 +2330,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C5" s="6">
         <v>4</v>
@@ -2706,7 +2347,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6">
         <v>3</v>
@@ -2724,7 +2365,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6">
         <v>5</v>
@@ -2741,7 +2382,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6">
         <v>4</v>
@@ -2759,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C9" s="14">
         <v>4</v>
@@ -2776,7 +2417,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C10" s="14">
         <v>4</v>
@@ -2793,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C11" s="14">
         <v>4</v>
@@ -2810,7 +2451,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C12" s="14">
         <v>4</v>
@@ -2827,7 +2468,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C13" s="14">
         <v>4</v>
@@ -2844,7 +2485,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C14" s="14">
         <v>4</v>
@@ -2861,7 +2502,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
@@ -2878,7 +2519,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C16" s="14">
         <v>4</v>
@@ -2891,15 +2532,15 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="59"/>
+      <c r="A17" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="56"/>
       <c r="C17" s="10">
         <v>60</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E17" s="19">
         <f>SUM(E2:E16)</f>
